--- a/PickleBall_Malicious_TP_FN.xlsx
+++ b/PickleBall_Malicious_TP_FN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ML_Project_2026\ACSAC\2.final_artifacts\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA29E644-D41E-4DE6-8CF3-4B83C8C60070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9C7B8C-478C-4F1B-A8B7-F7CB40E342DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCA21FD0-36A2-4902-8EAD-6747F24F8CD8}"/>
   </bookViews>
@@ -399,18 +399,6 @@
   <si>
     <t>Payload calls builtins.exec('a=7; b=10; print("Sum=", a+b)'), 
 which performs arithmetic and prints the result to stdout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payload calls __builtin__.eval(exec(...)) which prints "Hello, I am Gorden Ramsey!",
- imports os, and prints os.environ to stdout. </t>
-  </si>
-  <si>
-    <t>Payload calls __builtin__.compile(...) containing os.system("echo 'malicious code executed'").
-compile() only parses source into bytecode without executing it, and even if executed, the inner command is just an echo that prints a string to stdout.</t>
-  </si>
-  <si>
-    <t>Payload calls builtins.eval(...) which attempts urllib.request.urlopen
-('https://eozlys11waso3oz.m.pipedream.net'). The target domain is dead, so no outbound connection completes.</t>
   </si>
   <si>
     <t>Payload calls __builtin__.eval(exec('print("PWNED")')), which only prints the string "PWNED" to stdout.</t>
@@ -1378,6 +1366,16 @@
     <t xml:space="preserve">False Negative (Classified as Benign)
 </t>
   </si>
+  <si>
+    <t>Targets the same Pipedream endpoint as graniet/fwefwefwe/fwefwefwe/, but the payload has return at the start of the eval string. return is a statement, not an expression, and eval() in Python only accepts expressions. So it crashes with a SyntaxError: 'return' outside function before the network call is ever reached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payload calls __builtin__.eval(exec(...)) which prints "Hello, I am Gorden Ramsey!", and 
+ imports os, and prints os.environ to stdout. </t>
+  </si>
+  <si>
+    <t>Payload calls __builtin__.compile(...) containing os.system("echo 'malicious code executed'"). compile() only parses source into bytecode without executing it. If it is executed, it will call os.system() which spawns /bin/sh to run echo. That shell spawn would show up in syscall traces as execve("/bin/sh"), which should be flagged by ModelShield.</t>
+  </si>
 </sst>
 </file>
 
@@ -1419,7 +1417,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1477,6 +1475,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1554,7 +1558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1600,9 +1604,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1616,6 +1617,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1984,36 +1993,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.2" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="C1" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="53.4" customHeight="1">
-      <c r="A2" s="31"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="31"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>139</v>
+      <c r="E2" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>136</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>104</v>
@@ -2033,7 +2042,7 @@
         <v>106</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2047,7 +2056,7 @@
         <v>106</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2061,7 +2070,7 @@
         <v>106</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="2" customFormat="1">
@@ -2090,16 +2099,16 @@
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2113,16 +2122,16 @@
         <v>107</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2136,16 +2145,16 @@
         <v>107</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2159,16 +2168,16 @@
         <v>107</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2182,16 +2191,16 @@
         <v>107</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2205,16 +2214,16 @@
         <v>107</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2228,16 +2237,16 @@
         <v>107</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2278,17 +2287,17 @@
       <c r="C16" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>260</v>
+      <c r="E16" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>257</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" ht="66.599999999999994" customHeight="1">
@@ -2302,16 +2311,16 @@
         <v>107</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2325,16 +2334,16 @@
         <v>107</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" ht="43.2">
@@ -2348,16 +2357,16 @@
         <v>107</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1">
@@ -2385,7 +2394,7 @@
         <v>106</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>113</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="2" customFormat="1" ht="210" customHeight="1">
@@ -2399,21 +2408,21 @@
         <v>107</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F22" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="H22" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="2" customFormat="1" ht="187.2">
       <c r="A23" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>2</v>
@@ -2422,16 +2431,16 @@
         <v>107</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="2" customFormat="1">
@@ -2450,7 +2459,7 @@
     </row>
     <row r="25" spans="1:8" s="2" customFormat="1" ht="43.2">
       <c r="A25" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>2</v>
@@ -2459,12 +2468,12 @@
         <v>106</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>114</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="2" customFormat="1" ht="129.6">
       <c r="A26" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>20</v>
@@ -2473,16 +2482,16 @@
         <v>107</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="2" customFormat="1" ht="187.2">
@@ -2496,16 +2505,16 @@
         <v>107</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>162</v>
+        <v>158</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>159</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="2" customFormat="1" ht="91.8" customHeight="1">
@@ -2519,16 +2528,16 @@
         <v>107</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="2" customFormat="1" ht="86.4">
@@ -2542,16 +2551,16 @@
         <v>107</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="2" customFormat="1">
@@ -2579,19 +2588,19 @@
         <v>107</v>
       </c>
       <c r="E31" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="2" customFormat="1" ht="28.8">
+    </row>
+    <row r="32" spans="1:8" s="2" customFormat="1" ht="43.2">
       <c r="A32" s="2" t="s">
         <v>61</v>
       </c>
@@ -2602,7 +2611,7 @@
         <v>106</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>115</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="2" customFormat="1">
@@ -2630,7 +2639,7 @@
         <v>106</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="2" customFormat="1" ht="115.2">
@@ -2644,16 +2653,16 @@
         <v>107</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H35" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="2" customFormat="1">
@@ -2681,16 +2690,16 @@
         <v>107</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2704,7 +2713,7 @@
         <v>106</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2718,7 +2727,7 @@
         <v>106</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="2" customFormat="1" ht="43.2">
@@ -2732,16 +2741,16 @@
         <v>107</v>
       </c>
       <c r="E40" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -2754,8 +2763,8 @@
       <c r="C41" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="24" t="s">
-        <v>119</v>
+      <c r="D41" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="2" customFormat="1" ht="115.2">
@@ -2769,16 +2778,16 @@
         <v>107</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="2" customFormat="1">
@@ -2806,31 +2815,31 @@
         <v>106</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" s="2" customFormat="1" ht="216">
-      <c r="A45" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="28" customFormat="1" ht="216">
+      <c r="A45" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>261</v>
+      <c r="B45" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="31"/>
+      <c r="E45" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="H45" s="23" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2844,7 +2853,7 @@
         <v>106</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2858,30 +2867,30 @@
         <v>106</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="2" customFormat="1" ht="86.4">
-      <c r="A48" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="28" customFormat="1" ht="86.4">
+      <c r="A48" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>143</v>
+      <c r="C48" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="G48" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="2" customFormat="1" ht="72">
@@ -2895,16 +2904,16 @@
         <v>107</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="2" customFormat="1" ht="43.2">
@@ -2918,16 +2927,16 @@
         <v>107</v>
       </c>
       <c r="E50" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H50" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -2941,10 +2950,10 @@
         <v>106</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" s="2" customFormat="1" ht="28.8">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" s="9" customFormat="1" ht="28.8">
       <c r="A52" s="9" t="s">
         <v>80</v>
       </c>
@@ -2955,53 +2964,53 @@
         <v>106</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="2" customFormat="1" ht="259.2">
-      <c r="A53" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="28" customFormat="1" ht="259.2">
+      <c r="A53" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="7" t="s">
+      <c r="C53" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H53" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="7" t="s">
+    </row>
+    <row r="54" spans="1:8" s="28" customFormat="1" ht="86.4">
+      <c r="A54" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="F54" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="G54" s="28" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" s="2" customFormat="1" ht="86.4">
-      <c r="A54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E54" s="7" t="s">
+      <c r="H54" s="23" t="s">
         <v>200</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -3015,16 +3024,16 @@
         <v>107</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="2" customFormat="1">
@@ -3038,7 +3047,7 @@
         <v>106</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="5" customFormat="1" ht="57.6">
@@ -3051,17 +3060,17 @@
       <c r="C57" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E57" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="F57" s="27" t="s">
-        <v>208</v>
+      <c r="E57" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H57" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="2" customFormat="1">
@@ -3075,7 +3084,7 @@
         <v>106</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -3089,7 +3098,7 @@
         <v>106</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -3103,7 +3112,7 @@
         <v>106</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -3116,8 +3125,8 @@
       <c r="C61" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D61" s="28" t="s">
-        <v>206</v>
+      <c r="D61" s="27" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="2" customFormat="1" ht="43.2">
@@ -3131,16 +3140,16 @@
         <v>107</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G62" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H62" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="2" customFormat="1" ht="172.8">
@@ -3154,16 +3163,16 @@
         <v>107</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="2" customFormat="1" ht="158.4">
@@ -3177,16 +3186,16 @@
         <v>107</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3200,16 +3209,16 @@
         <v>107</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F65" s="26" t="s">
-        <v>230</v>
+        <v>215</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H65" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3223,16 +3232,16 @@
         <v>107</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F66" s="26" t="s">
-        <v>230</v>
+        <v>215</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3246,16 +3255,16 @@
         <v>107</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="F67" s="26" t="s">
-        <v>231</v>
+        <v>217</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>228</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H67" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3269,16 +3278,16 @@
         <v>107</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F68" s="26" t="s">
-        <v>232</v>
+        <v>218</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>229</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H68" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3292,16 +3301,16 @@
         <v>107</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F69" s="26" t="s">
-        <v>233</v>
+        <v>219</v>
+      </c>
+      <c r="F69" s="25" t="s">
+        <v>230</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H69" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3315,16 +3324,16 @@
         <v>107</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F70" s="26" t="s">
-        <v>234</v>
+        <v>219</v>
+      </c>
+      <c r="F70" s="25" t="s">
+        <v>231</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H70" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3338,16 +3347,16 @@
         <v>107</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F71" s="26" t="s">
-        <v>230</v>
+        <v>215</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H71" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3361,16 +3370,16 @@
         <v>107</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F72" s="26" t="s">
-        <v>230</v>
+        <v>215</v>
+      </c>
+      <c r="F72" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H72" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3384,16 +3393,16 @@
         <v>107</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="F73" s="26" t="s">
-        <v>235</v>
+        <v>220</v>
+      </c>
+      <c r="F73" s="25" t="s">
+        <v>232</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H73" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3407,16 +3416,16 @@
         <v>107</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>236</v>
+        <v>221</v>
+      </c>
+      <c r="F74" s="25" t="s">
+        <v>233</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H74" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -3430,7 +3439,7 @@
         <v>106</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="2" customFormat="1" ht="72">
@@ -3444,39 +3453,39 @@
         <v>107</v>
       </c>
       <c r="E76" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" s="28" customFormat="1" ht="115.2">
+      <c r="A77" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E77" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F77" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="G77" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="H76" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" s="2" customFormat="1" ht="115.2">
-      <c r="A77" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E77" s="7" t="s">
+      <c r="H77" s="28" t="s">
         <v>240</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="2" customFormat="1" ht="172.8">
@@ -3490,16 +3499,16 @@
         <v>107</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="2" customFormat="1" ht="86.4">
@@ -3513,16 +3522,16 @@
         <v>107</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="2" customFormat="1" ht="28.8">
@@ -3536,7 +3545,7 @@
         <v>106</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="2" customFormat="1" ht="43.2">
@@ -3550,16 +3559,16 @@
         <v>107</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="2" customFormat="1" ht="57.6">
@@ -3573,16 +3582,16 @@
         <v>107</v>
       </c>
       <c r="E82" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" t="s">
         <v>248</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="H82" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="83" spans="1:8" s="2" customFormat="1" ht="43.2">
@@ -3596,16 +3605,16 @@
         <v>107</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" spans="1:8" s="2" customFormat="1">
@@ -3633,21 +3642,21 @@
         <v>107</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:8" s="2" customFormat="1" ht="100.8">
       <c r="A86" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>47</v>
@@ -3656,16 +3665,16 @@
         <v>107</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
